--- a/Sajjad data/by_country_and_state/USA/PA.xlsx
+++ b/Sajjad data/by_country_and_state/USA/PA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1183" uniqueCount="535">
   <si>
     <t>Business Name</t>
   </si>
@@ -566,6 +566,1056 @@
   </si>
   <si>
     <t>2026-10-24T01:25:22.337Z</t>
+  </si>
+  <si>
+    <t>Advanced Cosmetic and Implant Dentistry</t>
+  </si>
+  <si>
+    <t>(484) 350-3239</t>
+  </si>
+  <si>
+    <t>501 N 17th St #107, Allentown, PA 18104</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Advanced+Cosmetic+and+Implant+Dentistry/data=!4m7!3m6!1s0x89c439884db9460f:0x8718013edd1efcf0!8m2!3d40.6039611!4d-75.4949594!16s%2Fg%2F1tff_fzx!19sChIJD0a5TYg5xIkR8Pwe3T4BGIc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T18:56:42.988Z</t>
+  </si>
+  <si>
+    <t>Allentown Emergency Dentistry</t>
+  </si>
+  <si>
+    <t>(484) 696-0816</t>
+  </si>
+  <si>
+    <t>413 N 13th St, Allentown, PA 18102</t>
+  </si>
+  <si>
+    <t>3.7</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Allentown+Emergency+Dentistry/data=!4m7!3m6!1s0x89c439715e9cd39b:0xc19729b8f89e012b!8m2!3d40.605239!4d-75.4864228!16s%2Fg%2F11rrp1qbp1!19sChIJm9OcXnE5xIkRKwGe-Lgpl8E?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T18:57:02.820Z</t>
+  </si>
+  <si>
+    <t>East Side Family Dentistry</t>
+  </si>
+  <si>
+    <t>(610) 776-7578</t>
+  </si>
+  <si>
+    <t>1640 Union Blvd, Allentown, PA 18109</t>
+  </si>
+  <si>
+    <t>2.6</t>
+  </si>
+  <si>
+    <t>Saturday9 AM–12 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/East+Side+Family+Dentistry/data=!4m7!3m6!1s0x89c43ed2f53d3a5d:0x1c079c7a73560615!8m2!3d40.6249959!4d-75.4313256!16s%2Fg%2F1td5mnb7!19sChIJXTo99dI-xIkRFQZWc3qcBxw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T18:57:29.601Z</t>
+  </si>
+  <si>
+    <t>Family Dentistry Abraham Imad DDS &amp; Associates</t>
+  </si>
+  <si>
+    <t>(610) 434-3310</t>
+  </si>
+  <si>
+    <t>1111 N 19th St, Allentown, PA 18104</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Family+Dentistry+Abraham+Imad+DDS+%26+Associates/data=!4m7!3m6!1s0x89c4398d345356bf:0x4af498d9b0a54ab!8m2!3d40.6119427!4d-75.5039595!16s%2Fg%2F1vtzj4g0!19sChIJv1ZTNI05xIkRq1QKm41JrwQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T18:58:08.649Z</t>
+  </si>
+  <si>
+    <t>Assali Family Dental Care</t>
+  </si>
+  <si>
+    <t>(610) 351-6285</t>
+  </si>
+  <si>
+    <t>1305 Hamilton St, Allentown, PA 18102</t>
+  </si>
+  <si>
+    <t>3.8</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Assali+Family+Dental+Care/data=!4m7!3m6!1s0x89c43a2a59304f6b:0x50e66b3daa66f2a6!8m2!3d40.5991162!4d-75.4842362!16s%2Fg%2F1w456k87!19sChIJa08wWSo6xIkRpvJmqj1r5lA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T18:58:11.327Z</t>
+  </si>
+  <si>
+    <t>Family Dentistry Of Allentown</t>
+  </si>
+  <si>
+    <t>(610) 295-6035</t>
+  </si>
+  <si>
+    <t>family dentistry</t>
+  </si>
+  <si>
+    <t>3300 Lehigh St, Allentown, PA 18103</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Family+Dentistry+Of+Allentown/data=!4m7!3m6!1s0x89c43afa1266dbc5:0xa452b03bf77c7b58!8m2!3d40.555824!4d-75.491921!16s%2Fg%2F11b6lm4mhp!19sChIJxdtmEvo6xIkRWHt89zuwUqQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T18:58:13.943Z</t>
+  </si>
+  <si>
+    <t>Smilekrafters Pediatric Dental Department</t>
+  </si>
+  <si>
+    <t>(267) 841-8705</t>
+  </si>
+  <si>
+    <t>1247 S Cedar Crest Blvd, Allentown, PA 18103</t>
+  </si>
+  <si>
+    <t>4.8</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Smilekrafters+Pediatric+Dental+Department/data=!4m7!3m6!1s0x89c43b37fce27633:0x2da543efd349acb7!8m2!3d40.5664095!4d-75.5147252!16s%2Fg%2F11h53wnd89!19sChIJM3bi_Dc7xIkRt6xJ0-9DpS0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T18:58:28.695Z</t>
+  </si>
+  <si>
+    <t>Dr. Matt H. Boswell, DMD</t>
+  </si>
+  <si>
+    <t>(610) 433-2357</t>
+  </si>
+  <si>
+    <t>3057 College Heights Blvd, Allentown, PA 18104</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Matt+H.+Boswell,+DMD/data=!4m7!3m6!1s0x89c43a08e7d35fa5:0xa1909f25a412954f!8m2!3d40.5941427!4d-75.5238902!16s%2Fg%2F1hc3sxk89!19sChIJpV_T5wg6xIkRT5USpCWfkKE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T18:58:31.285Z</t>
+  </si>
+  <si>
+    <t>Krafting Smile</t>
+  </si>
+  <si>
+    <t>(610) 437-5353</t>
+  </si>
+  <si>
+    <t>1901 Union Blvd, Allentown, PA 18109</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Krafting+Smile/data=!4m7!3m6!1s0x89c43b4305ab05ab:0x724ef3ac2eb926c1!8m2!3d40.6256886!4d-75.4277498!16s%2Fg%2F11s4b1ksn9!19sChIJqwWrBUM7xIkRwSa5LqzzTnI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T18:58:47.440Z</t>
+  </si>
+  <si>
+    <t>McKee Thomas J DMD</t>
+  </si>
+  <si>
+    <t>(610) 435-7727</t>
+  </si>
+  <si>
+    <t>1259 S Cedar Crest Blvd, Allentown, PA 18103</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>SaturdayClosed; SundayClosed; Monday9 AM–5 PM; Tuesday9 AM–5 PM; WednesdayClosed; Thursday9 AM–5 PM; Friday9 AM–5 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/McKee+Thomas+J+DMD/data=!4m7!3m6!1s0x89c43a87ee3f9b19:0x67b4e1f9af5394e9!8m2!3d40.5645327!4d-75.5170249!16s%2Fg%2F1tnjkj0t!19sChIJGZs_7oc6xIkR6ZRTr_nhtGc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T18:59:02.844Z</t>
+  </si>
+  <si>
+    <t>Dr. Sander White Emergency Dental Service</t>
+  </si>
+  <si>
+    <t>(610) 229-3800</t>
+  </si>
+  <si>
+    <t>1452 Tilghman St, Allentown, PA 18102</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Sander+White+Emergency+Dental+Service/data=!4m7!3m6!1s0x89c4396d37769869:0xf2dff8158fc63149!8m2!3d40.6071585!4d-75.492068!16s%2Fg%2F11zhfpgq9x!19sChIJaZh2N205xIkRSTHGjxX43_I?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T18:59:14.543Z</t>
+  </si>
+  <si>
+    <t>Hamilton Dental Associates</t>
+  </si>
+  <si>
+    <t>(610) 435-2550</t>
+  </si>
+  <si>
+    <t>1144 Hamilton St, Allentown, PA 18101</t>
+  </si>
+  <si>
+    <t>3.2</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Hamilton+Dental+Associates/data=!4m7!3m6!1s0x89c43a2ab59938ff:0xb34bdf8d1740a476!8m2!3d40.5993264!4d-75.4813604!16s%2Fg%2F1tcygdpx!19sChIJ_ziZtSo6xIkRdqRAF43fS7M?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T18:59:56.243Z</t>
+  </si>
+  <si>
+    <t>Robert Sanford</t>
+  </si>
+  <si>
+    <t>(610) 820-6000</t>
+  </si>
+  <si>
+    <t>1120 S Cedar Crest Blvd, Allentown, PA 181037990</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Robert+Sanford/data=!4m7!3m6!1s0x89c43a7bba700001:0x80ac74cbb50bf2b3!8m2!3d40.572255!4d-75.5198842!16s%2Fg%2F11pkfs22lg!19sChIJAQBwuns6xIkRs_ILtct0rIA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:00:52.494Z</t>
+  </si>
+  <si>
+    <t>Dr. Michael W. Schiffman, DMD</t>
+  </si>
+  <si>
+    <t>(610) 432-2841</t>
+  </si>
+  <si>
+    <t>1245 S Cedar Crest Blvd #204, Allentown, PA 18103</t>
+  </si>
+  <si>
+    <t>4.2</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Michael+W.+Schiffman,+DMD/data=!4m7!3m6!1s0x89c43a7d15eeeb89:0x1492c4078cc7fea7!8m2!3d40.5670036!4d-75.5157505!16s%2Fg%2F1tdkc031!19sChIJievuFX06xIkRp_7HjAfEkhQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:00:55.075Z</t>
+  </si>
+  <si>
+    <t>Sambuchino Richard R DDS</t>
+  </si>
+  <si>
+    <t>(814) 864-7511</t>
+  </si>
+  <si>
+    <t>4944 Peach St, Erie, PA 16509</t>
+  </si>
+  <si>
+    <t>Erie</t>
+  </si>
+  <si>
+    <t>4.3</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Sambuchino+Richard+R+DDS/data=!4m7!3m6!1s0x883280870b1f7da1:0x72eb4da94105479c!8m2!3d42.0818139!4d-80.0911974!16s%2Fg%2F1hc3g_4c5!19sChIJoX0fC4eAMogRnEcFQalN63I?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:01:10.821Z</t>
+  </si>
+  <si>
+    <t>Lehrian &amp; Palo Oral Surgery</t>
+  </si>
+  <si>
+    <t>(814) 454-3871</t>
+  </si>
+  <si>
+    <t>Oral surgeon</t>
+  </si>
+  <si>
+    <t>100 State St # B102, Erie, PA 16507</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Lehrian+%26+Palo+Oral+Surgery/data=!4m7!3m6!1s0x882d7ff039657867:0x2717489f65a42c04!8m2!3d42.1335133!4d-80.0887115!16s%2Fg%2F1wnbynhj!19sChIJZ3hlOfB_LYgRBCykZZ9IFyc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:01:13.611Z</t>
+  </si>
+  <si>
+    <t>Dr. James G. Di Loreto, DMD</t>
+  </si>
+  <si>
+    <t>(814) 455-5218</t>
+  </si>
+  <si>
+    <t>924 Peach St, Erie, PA 16501</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+James+G.+Di+Loreto,+DMD/data=!4m7!3m6!1s0x882d7fe30b16a995:0x94952645000dcc84!8m2!3d42.1251912!4d-80.0843778!16s%2Fg%2F1thlnqkf!19sChIJlakWC-N_LYgRhMwNAEUmlZQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:01:18.514Z</t>
+  </si>
+  <si>
+    <t>Dr. William D. Morosky, DMD, FAGD, MAGD</t>
+  </si>
+  <si>
+    <t>(814) 838-3045</t>
+  </si>
+  <si>
+    <t>4045 W 12th St, Erie, PA 16505</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+William+D.+Morosky,+DMD,+FAGD,+MAGD/data=!4m7!3m6!1s0x88327ed8621f64cf:0xfe26f602c8fdce1b!8m2!3d42.0890771!4d-80.1736978!16s%2Fg%2F1thfg2jm!19sChIJz2QfYth-MogRG879yAL2Jv4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:01:22.804Z</t>
+  </si>
+  <si>
+    <t>Dr. Michael J. Rahner, DMD</t>
+  </si>
+  <si>
+    <t>(814) 838-9237</t>
+  </si>
+  <si>
+    <t>4020 Sterrettania Rd, Erie, PA 16506</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Michael+J.+Rahner,+DMD/data=!4m7!3m6!1s0x88327ef4fc7c0235:0x85307aa4f6394377!8m2!3d42.0701055!4d-80.1460983!16s%2Fg%2F1tfv162j!19sChIJNQJ8_PR-MogRd0M59qR6MIU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:01:31.232Z</t>
+  </si>
+  <si>
+    <t>Dr. Adam Hammerlee</t>
+  </si>
+  <si>
+    <t>(814) 868-3647</t>
+  </si>
+  <si>
+    <t>5158 Peach St, Erie, PA 16509</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Adam+Hammerlee/data=!4m7!3m6!1s0x88328086a99d5053:0xede1dd219f2ce2b4!8m2!3d42.0784188!4d-80.0922065!16s%2Fg%2F11qgb79yrw!19sChIJU1CdqYaAMogRtOIsnyHd4e0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:01:33.782Z</t>
+  </si>
+  <si>
+    <t>Hissom James a DDS</t>
+  </si>
+  <si>
+    <t>(814) 835-8300</t>
+  </si>
+  <si>
+    <t>2330 W 38th St, Erie, PA 16506</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Hissom+James+a+DDS/data=!4m7!3m6!1s0x88327e3584bc039d:0xa7fd04a94eb60412!8m2!3d42.08276!4d-80.119888!16s%2Fg%2F1tf43m36!19sChIJnQO8hDV-MogREgS2TqkE_ac?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:01:36.151Z</t>
+  </si>
+  <si>
+    <t>Borst Jeffery A DDS</t>
+  </si>
+  <si>
+    <t>(814) 315-2738</t>
+  </si>
+  <si>
+    <t>128 W 9th St, Erie, PA 16501</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Borst+Jeffery+A+DDS/data=!4m7!3m6!1s0x882d7fe341c53379:0x435d4f3b2f6a02fa!8m2!3d42.1257141!4d-80.0857772!16s%2Fg%2F1tfqgfs6!19sChIJeTPFQeN_LYgR-gJqLztPXUM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:01:53.489Z</t>
+  </si>
+  <si>
+    <t>Emergency Dentist Assistance</t>
+  </si>
+  <si>
+    <t>(814) 259-9393</t>
+  </si>
+  <si>
+    <t>3123 W 12th St, Erie, PA 16505</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Emergency+Dentist+Assistance/data=!4m7!3m6!1s0x88327fe83f4e926d:0x7abda311968eca52!8m2!3d42.0968953!4d-80.1521429!16s%2Fg%2F11zy8_58q0!19sChIJbZJOP-h_MogRUsqOlhGjvXo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:01:56.484Z</t>
+  </si>
+  <si>
+    <t>Wilcko, M. Thomas DMD</t>
+  </si>
+  <si>
+    <t>(814) 868-3669</t>
+  </si>
+  <si>
+    <t>Denture care center</t>
+  </si>
+  <si>
+    <t>3736 Sterrettania Rd, Erie, PA 16506</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>SaturdayClosed; SundayClosed; Monday8 AM–5 PM; Tuesday8 AM–5 PM; Wednesday8 AM–12 PM; Thursday8 AM–5 PM; Friday9 AM–12 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Wilcko,+M.+Thomas+DMD/data=!4m7!3m6!1s0x883280a1bb724193:0x95bfb944cedd011a!8m2!3d42.0743646!4d-80.1441449!16s%2Fg%2F1wf22hpf!19sChIJk0Fyu6GAMogRGgHdzkS5v5U?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:01:59.536Z</t>
+  </si>
+  <si>
+    <t>Radack III Stephen T DDS</t>
+  </si>
+  <si>
+    <t>(814) 825-6221</t>
+  </si>
+  <si>
+    <t>3822 Wayne St, Erie, PA 16546</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Radack+III+Stephen+T+DDS/data=!4m7!3m6!1s0x883280338d512495:0x61af6f981f3621cf!8m2!3d42.1076415!4d-80.0491975!16s%2Fg%2F1tfpvxyg!19sChIJlSRRjTOAMogRzyE2H5hvr2E?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:02:01.642Z</t>
+  </si>
+  <si>
+    <t>Sarbak John J DDS</t>
+  </si>
+  <si>
+    <t>(814) 868-3118</t>
+  </si>
+  <si>
+    <t>936 W 38th St, Erie, PA 16508</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Sarbak+John+J+DDS/data=!4m7!3m6!1s0x8832806e2af05cf3:0x1c891ece9837e6b9!8m2!3d42.0950649!4d-80.0868647!16s%2Fg%2F1tdm8zqp!19sChIJ81zwKm6AMogRueY3mM4eiRw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:02:04.755Z</t>
+  </si>
+  <si>
+    <t>Trice William B DDS</t>
+  </si>
+  <si>
+    <t>(814) 455-5116</t>
+  </si>
+  <si>
+    <t>1611 Peach St #275, Erie, PA 16501</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Trice+William+B+DDS/data=!4m7!3m6!1s0x8832801e42c6439d:0xfdf4c53673dcc7fd!8m2!3d42.1196112!4d-80.0796397!16s%2Fg%2F1tfx5jzk!19sChIJnUPGQh6AMogR_cfcczbF9P0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:02:07.114Z</t>
+  </si>
+  <si>
+    <t>American Academy-Pediatric</t>
+  </si>
+  <si>
+    <t>(814) 868-8673</t>
+  </si>
+  <si>
+    <t>128 W 12th St #300, Erie, PA 16501</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/American+Academy-Pediatric/data=!4m7!3m6!1s0x882d7fe2673dced7:0x31233ed50a4248f8!8m2!3d42.1229121!4d-80.0839375!16s%2Fg%2F1v29cnwz!19sChIJ1849Z-J_LYgR-EhCCtU-IzE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:04:05.684Z</t>
+  </si>
+  <si>
+    <t>Drew Carlin</t>
+  </si>
+  <si>
+    <t>(814) 455-2158</t>
+  </si>
+  <si>
+    <t>3219 Peach St, Erie, PA 165082735</t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Drew+Carlin/data=!4m7!3m6!1s0x883280150fcff41d:0x280c53305359d82d!8m2!3d42.1033933!4d-80.0778268!16s%2Fg%2F11pkfqkvqr!19sChIJHfTPDxWAMogRLdhZUzBTDCg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:04:08.300Z</t>
+  </si>
+  <si>
+    <t>Romeo Robert L DMD</t>
+  </si>
+  <si>
+    <t>(814) 833-0282</t>
+  </si>
+  <si>
+    <t>2634 W 30th St, Erie, PA 16506</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Romeo+Robert+L+DMD/data=!4m7!3m6!1s0x88327ee96f33ad0f:0x54188fb1971d919d!8m2!3d42.0870669!4d-80.130698!16s%2Fg%2F1tfd314b!19sChIJD60zb-l-MogRnZEdl7GPGFQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:04:12.768Z</t>
+  </si>
+  <si>
+    <t>Miller Denise</t>
+  </si>
+  <si>
+    <t>(814) 868-5449</t>
+  </si>
+  <si>
+    <t>3822 Schaper Ave #1, Erie, PA 16508</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Miller+Denise/data=!4m7!3m6!1s0x88327e333be691b3:0x7de99e4758fa065f!8m2!3d42.0839267!4d-80.1136005!16s%2Fg%2F1ttphjwd!19sChIJs5HmOzN-MogRXwb6WEee6X0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:04:39.233Z</t>
+  </si>
+  <si>
+    <t>Dr. Ronald Merski</t>
+  </si>
+  <si>
+    <t>(814) 825-6648</t>
+  </si>
+  <si>
+    <t>4404 Dexter Ave., Erie, PA 16504</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Ronald+Merski/data=!4m7!3m6!1s0x883281c32e1d6d39:0x9d0f0af45039a952!8m2!3d42.1071782!4d-80.0346417!16s%2Fg%2F11qgb79w1x!19sChIJOW0dLsOBMogRUqk5UPQKD50?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:04:41.774Z</t>
+  </si>
+  <si>
+    <t>Michael Moore</t>
+  </si>
+  <si>
+    <t>(814) 833-4393</t>
+  </si>
+  <si>
+    <t>2606 Caughey Rd, Erie, PA 165062148</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Michael+Moore/data=!4m7!3m6!1s0x88327ee5272bffff:0xf7630a70a25a91fc!8m2!3d42.0811273!4d-80.1550475!16s%2Fg%2F11pkfrvt4k!19sChIJ__8rJ-V-MogR_JFaonAKY_c?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:04:46.116Z</t>
+  </si>
+  <si>
+    <t>Your clinic here: Now Available</t>
+  </si>
+  <si>
+    <t>(814) 456-6935</t>
+  </si>
+  <si>
+    <t>Medical office</t>
+  </si>
+  <si>
+    <t>1351 W 6th St, Erie, PA 16505</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Your+clinic+here:+Now+Available/data=!4m7!3m6!1s0x88327ff400956d2d:0x21fda0c8799e248c!8m2!3d42.1191485!4d-80.1154093!16s%2Fg%2F1tqclw8g!19sChIJLW2VAPR_MogRjCSeecig_SE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:05:48.012Z</t>
+  </si>
+  <si>
+    <t>West Lake Dental Arts</t>
+  </si>
+  <si>
+    <t>(814) 833-3001</t>
+  </si>
+  <si>
+    <t>3437 W Lake Rd, Erie, PA 16505</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/West+Lake+Dental+Arts/data=!4m7!3m6!1s0x88327f17c126bb39:0xa3019974240932c8!8m2!3d42.1004199!4d-80.1638464!16s%2Fg%2F1trc5m1j!19sChIJObsmwRd_MogRyDIJJHSZAaM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:05:54.936Z</t>
+  </si>
+  <si>
+    <t>Swanson Jeffrey DDS</t>
+  </si>
+  <si>
+    <t>(814) 454-3001</t>
+  </si>
+  <si>
+    <t>1611 Peach St #250, Erie, PA 16501</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Swanson+Jeffrey+DDS/data=!4m7!3m6!1s0x8832801e42c6439d:0xfbff33bebebc1985!8m2!3d42.119582!4d-80.0796374!16s%2Fg%2F1tn4ytjh!19sChIJnUPGQh6AMogRhRm8vr4z__s?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:06:06.236Z</t>
+  </si>
+  <si>
+    <t>Dr. John W. Cerminara, DDS</t>
+  </si>
+  <si>
+    <t>(814) 452-1632</t>
+  </si>
+  <si>
+    <t>1341 W 26th St #100, Erie, PA 16508</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+John+W.+Cerminara,+DDS/data=!4m7!3m6!1s0x88327fde5738c805:0xc854d0a0ae991b2e!8m2!3d42.1012394!4d-80.1015666!16s%2Fg%2F1tfbjcl0!19sChIJBcg4V95_MogRLhuZrqDQVMg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:06:08.390Z</t>
+  </si>
+  <si>
+    <t>Joseph Hans F Do</t>
+  </si>
+  <si>
+    <t>(814) 864-4031</t>
+  </si>
+  <si>
+    <t>Periodontist</t>
+  </si>
+  <si>
+    <t>5515 Peach St, Erie, PA 16509</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Joseph+Hans+F+Do/data=!4m7!3m6!1s0x8832808349296c81:0xc39138676d1e2145!8m2!3d42.0739522!4d-80.0935705!16s%2Fg%2F1tfxhbfx!19sChIJgWwpSYOAMogRRSEebWc4kcM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:06:10.876Z</t>
+  </si>
+  <si>
+    <t>Pierce Daryl T DMD</t>
+  </si>
+  <si>
+    <t>(814) 897-1277</t>
+  </si>
+  <si>
+    <t>4626 Buffalo Rd, Erie, PA 16510</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Pierce+Daryl+T+DMD/data=!4m7!3m6!1s0x882d7dd204143a03:0xa329798e8777bd7c!8m2!3d42.1489715!4d-79.9985504!16s%2Fg%2F1td26261!19sChIJAzoUBNJ9LYgRfL13h455KaM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:06:13.678Z</t>
+  </si>
+  <si>
+    <t>Glecos &amp; Glecos</t>
+  </si>
+  <si>
+    <t>(814) 459-1608</t>
+  </si>
+  <si>
+    <t>3408 State St, Erie, PA 16508</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Glecos+%26+Glecos/data=!4m7!3m6!1s0x8832803950f7b6c9:0xc64388b9c8e3648b!8m2!3d42.1052998!4d-80.0697163!16s%2Fg%2F1vq75hxd!19sChIJybb3UDmAMogRi2TjyLmIQ8Y?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:06:16.443Z</t>
+  </si>
+  <si>
+    <t>Dr. Christopher Demarco</t>
+  </si>
+  <si>
+    <t>(814) 456-0710</t>
+  </si>
+  <si>
+    <t>333 State St Suite 310, Erie, PA 16507</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Christopher+Demarco/data=!4m7!3m6!1s0x882d7feffa169f9f:0x505520ca015db1d9!8m2!3d42.1319965!4d-80.0863884!16s%2Fg%2F11p079qrpm!19sChIJn58W-u9_LYgR2bFdAcogVVA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:06:18.947Z</t>
+  </si>
+  <si>
+    <t>Reading Dental Specialty</t>
+  </si>
+  <si>
+    <t>(844) 817-0066</t>
+  </si>
+  <si>
+    <t>2230 N 5th Street Hwy Ste 104, Reading, PA 19605</t>
+  </si>
+  <si>
+    <t>Reading</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Reading+Dental+Specialty/data=!4m7!3m6!1s0x89c67790097deccb:0x318c8fbf1f27a0a1!8m2!3d40.3690694!4d-75.9272503!16s%2Fg%2F11sn_zw_nd!19sChIJy-x9CZB3xokRoaAnH7-PjDE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:06:33.994Z</t>
+  </si>
+  <si>
+    <t>Penn Dental: Safwan Shaaya DDS INC</t>
+  </si>
+  <si>
+    <t>(610) 374-0906</t>
+  </si>
+  <si>
+    <t>1027 Penn St, Reading, PA 19601</t>
+  </si>
+  <si>
+    <t>3.9</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Penn+Dental:+Safwan+Shaaya+DDS+INC/data=!4m7!3m6!1s0x89c670b3567af19d:0x9d324a6295a030f2!8m2!3d40.3353273!4d-75.9171535!16s%2Fg%2F1tj97c3h!19sChIJnfF6VrNwxokR8jCglWJKMp0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:06:36.959Z</t>
+  </si>
+  <si>
+    <t>Dr. Kami Hazaveh, DMD</t>
+  </si>
+  <si>
+    <t>(610) 779-0911</t>
+  </si>
+  <si>
+    <t>501 Carsonia Ave, Reading, PA 19606</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Kami+Hazaveh,+DMD/data=!4m7!3m6!1s0x89c679f701f5214d:0x2cabfddf575dcb56!8m2!3d40.3346941!4d-75.8854537!16s%2Fg%2F1v1kqtk4!19sChIJTSH1Afd5xokRVstdV9_9qyw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:06:41.061Z</t>
+  </si>
+  <si>
+    <t>Life Changing Dental Center</t>
+  </si>
+  <si>
+    <t>(844) 255-6636</t>
+  </si>
+  <si>
+    <t>3607 Perkiomen Ave, Reading, PA 19606</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Life+Changing+Dental+Center/data=!4m7!3m6!1s0x89c67a3ce328236d:0xa479f4b5c028a4b8!8m2!3d40.3185998!4d-75.8735401!16s%2Fg%2F1wg5yzbz!19sChIJbSMo4zx6xokRuKQowLX0eaQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:06:43.782Z</t>
+  </si>
+  <si>
+    <t>Shelbourne Dental Care</t>
+  </si>
+  <si>
+    <t>(610) 779-0610</t>
+  </si>
+  <si>
+    <t>1270 Shelbourne Rd, Reading, PA 19606</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Shelbourne+Dental+Care/data=!4m7!3m6!1s0x89c67bd45f8adb8f:0xf7310b3a4e0db510!8m2!3d40.3238388!4d-75.8504455!16s%2Fg%2F1tdy5dxd!19sChIJj9uKX9R7xokRELUNTjoLMfc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:06:46.356Z</t>
+  </si>
+  <si>
+    <t>Kosenske Christopher DDS</t>
+  </si>
+  <si>
+    <t>(610) 378-2445</t>
+  </si>
+  <si>
+    <t>145 N 6th St, Reading, PA 19601</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Kosenske+Christopher+DDS/data=!4m7!3m6!1s0x89c6773526d8bc71:0x96d2a33c9ed1101c!8m2!3d40.3380229!4d-75.9253027!16s%2Fg%2F1tfjrnpg!19sChIJcbzYJjV3xokRHBDRnjyj0pY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:06:49.195Z</t>
+  </si>
+  <si>
+    <t>Penn Square Dental Care</t>
+  </si>
+  <si>
+    <t>(610) 374-4150</t>
+  </si>
+  <si>
+    <t>13 N 5th St, Reading, PA 19601</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Penn+Square+Dental+Care/data=!4m7!3m6!1s0x89c670cb405c0a19:0xc3cc20883e091543!8m2!3d40.335994!4d-75.927566!16s%2Fg%2F1tvm3qj6!19sChIJGQpcQMtwxokRQxUJPoggzMM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:06:51.968Z</t>
+  </si>
+  <si>
+    <t>Hometown Dental Care</t>
+  </si>
+  <si>
+    <t>(610) 987-8008</t>
+  </si>
+  <si>
+    <t>1064 Memorial Hwy, Oley, PA 19547</t>
+  </si>
+  <si>
+    <t>Oley</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Hometown+Dental+Care/data=!4m7!3m6!1s0x89c67f45c618e445:0xef7d92f45d70704a!8m2!3d40.3858261!4d-75.7930221!16s%2Fg%2F1th6fs_b!19sChIJReQYxkV_xokRSnBwXfSSfe8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:07:06.493Z</t>
+  </si>
+  <si>
+    <t>Robert Zalitchi, DMD, Adamstown Family Dentistry</t>
+  </si>
+  <si>
+    <t>(717) 484-0707</t>
+  </si>
+  <si>
+    <t>2726 N Reading Rd, Reinholds, PA 17569</t>
+  </si>
+  <si>
+    <t>Reinholds</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Robert+Zalitchi,+DMD,+Adamstown+Family+Dentistry/data=!4m7!3m6!1s0x89c66d28257c737f:0xd8686ec6f4c79b90!8m2!3d40.2355753!4d-76.0760954!16s%2Fg%2F1tj1ngm_!19sChIJf3N8JShtxokRkJvH9MZuaNg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:07:17.617Z</t>
+  </si>
+  <si>
+    <t>Birdsboro Family Dental Associates</t>
+  </si>
+  <si>
+    <t>(610) 582-1594</t>
+  </si>
+  <si>
+    <t>349 W Main St, Birdsboro, PA 19508</t>
+  </si>
+  <si>
+    <t>Birdsboro</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Birdsboro+Family+Dental+Associates/data=!4m7!3m6!1s0x89c67b660730e657:0x5c0585ca9d60ff88!8m2!3d40.2683214!4d-75.8182956!16s%2Fg%2F1tdq_ny4!19sChIJV-YwB2Z7xokRiP9gncqFBVw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:07:22.315Z</t>
+  </si>
+  <si>
+    <t>West Reading Family &amp; Cosmetic</t>
+  </si>
+  <si>
+    <t>(610) 376-4384</t>
+  </si>
+  <si>
+    <t>721 Penn Ave, West Reading, PA 19611</t>
+  </si>
+  <si>
+    <t>West Reading</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/West+Reading+Family+%26+Cosmetic/data=!4m7!3m6!1s0x89c6712c0dacfdc3:0x15acc63cab034696!8m2!3d40.3361974!4d-75.9527025!16s%2Fg%2F1tlc905c!19sChIJw_2sDSxxxokRlkYDqzzGrBU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:07:25.066Z</t>
+  </si>
+  <si>
+    <t>Sweitzer &amp; Zillhardt Family</t>
+  </si>
+  <si>
+    <t>(610) 779-7444</t>
+  </si>
+  <si>
+    <t>20 N 23rd St, Reading, PA 19606</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Sweitzer+%26+Zillhardt+Family/data=!4m7!3m6!1s0x89c67a0390cf4ce5:0xb3864b310244c49!8m2!3d40.3286151!4d-75.8920028!16s%2Fg%2F1vn_zxq9!19sChIJ5UzPkAN6xokRSUwkELNkOAs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:07:27.873Z</t>
+  </si>
+  <si>
+    <t>David M Causa DDS</t>
+  </si>
+  <si>
+    <t>(610) 777-1001</t>
+  </si>
+  <si>
+    <t>206 Revere Blvd, West Lawn, PA 19609</t>
+  </si>
+  <si>
+    <t>West Lawn</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/David+M+Causa+DDS/data=!4m7!3m6!1s0x89c6717bf09a62dd:0x9c193463c2db0341!8m2!3d40.3099968!4d-75.9864591!16s%2Fg%2F1vq75tfh!19sChIJ3WKa8HtxxokRQQPbwmM0GZw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:07:42.397Z</t>
+  </si>
+  <si>
+    <t>Dr. John H. Muhr, DMD</t>
+  </si>
+  <si>
+    <t>(610) 376-2857</t>
+  </si>
+  <si>
+    <t>Prosthodontist</t>
+  </si>
+  <si>
+    <t>616 Reading Ave, Reading, PA 19611</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+John+H.+Muhr,+DMD/data=!4m7!3m6!1s0x89c6712bbb87d289:0xd529a0ea28d32e88!8m2!3d40.3367127!4d-75.9502932!16s%2Fg%2F1tf32b7b!19sChIJidKHuytxxokRiC7TKOqgKdU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:07:45.272Z</t>
+  </si>
+  <si>
+    <t>Dr.Schnieder-Implant Specialist</t>
+  </si>
+  <si>
+    <t>(484) 713-6766</t>
+  </si>
+  <si>
+    <t>1901 #2 Bernville Rd, Reading, PA 19601</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.Schnieder-Implant+Specialist/data=!4m7!3m6!1s0x89c676e6f21edefd:0x173e3d89ecb2ba23!8m2!3d40.3639884!4d-75.9542118!16s%2Fg%2F1thq672q!19sChIJ_d4e8uZ2xokRI7qy7Ik9Phc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:08:15.273Z</t>
+  </si>
+  <si>
+    <t>Dr. Paul R. Farrell, DMD</t>
+  </si>
+  <si>
+    <t>(610) 777-7646</t>
+  </si>
+  <si>
+    <t>517 E Lancaster Ave, Shillington, PA 19607</t>
+  </si>
+  <si>
+    <t>Shillington</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Paul+R.+Farrell,+DMD/data=!4m7!3m6!1s0x89c6710582f58e6b:0xa661424d214977fb!8m2!3d40.3081254!4d-75.9573375!16s%2Fg%2F1td5mnh9!19sChIJa471ggVxxokR-3dJIU1CYaY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:08:19.919Z</t>
+  </si>
+  <si>
+    <t>Fries &amp; Fries</t>
+  </si>
+  <si>
+    <t>(610) 777-4907</t>
+  </si>
+  <si>
+    <t>403 W Lancaster Ave, Shillington, PA 19607</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Fries+%26+Fries/data=!4m7!3m6!1s0x89c6717431144a5b:0x327754f870034d1f!8m2!3d40.3056841!4d-75.9743982!16s%2Fg%2F113fb79vb!19sChIJW0oUMXRxxokRH00DcPhUdzI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:08:22.555Z</t>
+  </si>
+  <si>
+    <t>Sheikh Emmad S DDS</t>
+  </si>
+  <si>
+    <t>(610) 378-2440</t>
+  </si>
+  <si>
+    <t>145 N 6th St #2, Reading, PA 19601</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Sheikh+Emmad+S+DDS/data=!4m7!3m6!1s0x89c6773526d8a4ab:0x837e2f77dfbddaaf!8m2!3d40.3380229!4d-75.9253027!16s%2Fg%2F1260brhcl!19sChIJq6TYJjV3xokRr9q933cvfoM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:08:39.617Z</t>
+  </si>
+  <si>
+    <t>Cyril V Leddy PC</t>
+  </si>
+  <si>
+    <t>(610) 372-7218</t>
+  </si>
+  <si>
+    <t>312 Lancaster Ave, Reading, PA 19611</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Cyril+V+Leddy+PC/data=!4m7!3m6!1s0x89c67b5fc7c3c58b:0x461a4f504a200d44!8m2!3d40.3213854!4d-75.9339684!16s%2Fg%2F1v_s6v3x!19sChIJi8XDx197xokRRA0gSlBPGkY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:08:57.126Z</t>
+  </si>
+  <si>
+    <t>Dentists In Reading Pa</t>
+  </si>
+  <si>
+    <t>(610) 488-2051</t>
+  </si>
+  <si>
+    <t>4900 Green Tree Rd # 140, Reading, PA 19606</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dentists+In+Reading+Pa/data=!4m7!3m6!1s0x89c67a4c24cb3665:0xc15a31f6656b066!8m2!3d40.3017824!4d-75.8584155!16s%2Fg%2F12613ysc7!19sChIJZTbLJEx6xokRZrBWZh-jFQw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:09:00.249Z</t>
+  </si>
+  <si>
+    <t>Ronald C. Szish DDS</t>
+  </si>
+  <si>
+    <t>(610) 921-2336</t>
+  </si>
+  <si>
+    <t>3330 Plaza Dr, Reading, PA 19605</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Ronald+C.+Szish+DDS/data=!4m7!3m6!1s0x89c677a4621d3bef:0x6a38cf57ce37dcf1!8m2!3d40.3849583!4d-75.9297076!16s%2Fg%2F1td5y2zz!19sChIJ7zsdYqR3xokR8dw3zlfPOGo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:09:04.762Z</t>
+  </si>
+  <si>
+    <t>Mark Dougherty</t>
+  </si>
+  <si>
+    <t>(610) 374-7657</t>
+  </si>
+  <si>
+    <t>645 Penn Ave, West Reading, PA 19611</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Mark+Dougherty/data=!4m7!3m6!1s0x89c6712bf28c0001:0x8917d363c7e26292!8m2!3d40.3361739!4d-75.9514819!16s%2Fg%2F11pkfqx6n0!19sChIJAQCM8itxxokRkmLix2PTF4k?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:09:09.288Z</t>
+  </si>
+  <si>
+    <t>Temple Dental Arts LLC</t>
+  </si>
+  <si>
+    <t>(610) 921-8129</t>
+  </si>
+  <si>
+    <t>4729 Kutztown Rd, Temple, PA 19560</t>
+  </si>
+  <si>
+    <t>Temple</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Temple+Dental+Arts+LLC/data=!4m7!3m6!1s0x89c677e62e8c9935:0xe8180c89d014d8b0!8m2!3d40.4065722!4d-75.9198608!16s%2Fg%2F1td1qvbp!19sChIJNZmMLuZ3xokRsNgU0IkMGOg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:09:34.182Z</t>
   </si>
 </sst>
 </file>
@@ -946,7 +1996,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M91"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -2070,6 +3120,2630 @@
         <v>184</v>
       </c>
     </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>185</v>
+      </c>
+      <c r="B28" t="s">
+        <v>186</v>
+      </c>
+      <c r="C28" t="s">
+        <v>35</v>
+      </c>
+      <c r="D28" t="s">
+        <v>187</v>
+      </c>
+      <c r="E28" t="s">
+        <v>180</v>
+      </c>
+      <c r="F28" t="s">
+        <v>18</v>
+      </c>
+      <c r="G28" t="s">
+        <v>19</v>
+      </c>
+      <c r="H28" t="s">
+        <v>29</v>
+      </c>
+      <c r="I28" t="s">
+        <v>21</v>
+      </c>
+      <c r="J28" t="s">
+        <v>30</v>
+      </c>
+      <c r="K28" t="s">
+        <v>23</v>
+      </c>
+      <c r="L28" t="s">
+        <v>188</v>
+      </c>
+      <c r="M28" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>190</v>
+      </c>
+      <c r="B29" t="s">
+        <v>191</v>
+      </c>
+      <c r="C29" t="s">
+        <v>134</v>
+      </c>
+      <c r="D29" t="s">
+        <v>192</v>
+      </c>
+      <c r="E29" t="s">
+        <v>180</v>
+      </c>
+      <c r="F29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G29" t="s">
+        <v>19</v>
+      </c>
+      <c r="H29" t="s">
+        <v>193</v>
+      </c>
+      <c r="I29" t="s">
+        <v>21</v>
+      </c>
+      <c r="J29" t="s">
+        <v>88</v>
+      </c>
+      <c r="K29" t="s">
+        <v>23</v>
+      </c>
+      <c r="L29" t="s">
+        <v>194</v>
+      </c>
+      <c r="M29" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>196</v>
+      </c>
+      <c r="B30" t="s">
+        <v>197</v>
+      </c>
+      <c r="C30" t="s">
+        <v>35</v>
+      </c>
+      <c r="D30" t="s">
+        <v>198</v>
+      </c>
+      <c r="E30" t="s">
+        <v>180</v>
+      </c>
+      <c r="F30" t="s">
+        <v>18</v>
+      </c>
+      <c r="G30" t="s">
+        <v>19</v>
+      </c>
+      <c r="H30" t="s">
+        <v>199</v>
+      </c>
+      <c r="I30" t="s">
+        <v>21</v>
+      </c>
+      <c r="J30" t="s">
+        <v>200</v>
+      </c>
+      <c r="K30" t="s">
+        <v>23</v>
+      </c>
+      <c r="L30" t="s">
+        <v>201</v>
+      </c>
+      <c r="M30" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>203</v>
+      </c>
+      <c r="B31" t="s">
+        <v>204</v>
+      </c>
+      <c r="C31" t="s">
+        <v>35</v>
+      </c>
+      <c r="D31" t="s">
+        <v>205</v>
+      </c>
+      <c r="E31" t="s">
+        <v>180</v>
+      </c>
+      <c r="F31" t="s">
+        <v>18</v>
+      </c>
+      <c r="G31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H31" t="s">
+        <v>67</v>
+      </c>
+      <c r="I31" t="s">
+        <v>21</v>
+      </c>
+      <c r="J31" t="s">
+        <v>30</v>
+      </c>
+      <c r="K31" t="s">
+        <v>23</v>
+      </c>
+      <c r="L31" t="s">
+        <v>206</v>
+      </c>
+      <c r="M31" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>208</v>
+      </c>
+      <c r="B32" t="s">
+        <v>209</v>
+      </c>
+      <c r="C32" t="s">
+        <v>35</v>
+      </c>
+      <c r="D32" t="s">
+        <v>210</v>
+      </c>
+      <c r="E32" t="s">
+        <v>180</v>
+      </c>
+      <c r="F32" t="s">
+        <v>18</v>
+      </c>
+      <c r="G32" t="s">
+        <v>19</v>
+      </c>
+      <c r="H32" t="s">
+        <v>211</v>
+      </c>
+      <c r="I32" t="s">
+        <v>21</v>
+      </c>
+      <c r="J32" t="s">
+        <v>30</v>
+      </c>
+      <c r="K32" t="s">
+        <v>23</v>
+      </c>
+      <c r="L32" t="s">
+        <v>212</v>
+      </c>
+      <c r="M32" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>214</v>
+      </c>
+      <c r="B33" t="s">
+        <v>215</v>
+      </c>
+      <c r="C33" t="s">
+        <v>216</v>
+      </c>
+      <c r="D33" t="s">
+        <v>217</v>
+      </c>
+      <c r="E33" t="s">
+        <v>180</v>
+      </c>
+      <c r="F33" t="s">
+        <v>18</v>
+      </c>
+      <c r="G33" t="s">
+        <v>19</v>
+      </c>
+      <c r="H33" t="s">
+        <v>193</v>
+      </c>
+      <c r="I33" t="s">
+        <v>21</v>
+      </c>
+      <c r="J33" t="s">
+        <v>88</v>
+      </c>
+      <c r="K33" t="s">
+        <v>23</v>
+      </c>
+      <c r="L33" t="s">
+        <v>218</v>
+      </c>
+      <c r="M33" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>220</v>
+      </c>
+      <c r="B34" t="s">
+        <v>221</v>
+      </c>
+      <c r="C34" t="s">
+        <v>47</v>
+      </c>
+      <c r="D34" t="s">
+        <v>222</v>
+      </c>
+      <c r="E34" t="s">
+        <v>180</v>
+      </c>
+      <c r="F34" t="s">
+        <v>18</v>
+      </c>
+      <c r="G34" t="s">
+        <v>19</v>
+      </c>
+      <c r="H34" t="s">
+        <v>223</v>
+      </c>
+      <c r="I34" t="s">
+        <v>21</v>
+      </c>
+      <c r="J34" t="s">
+        <v>30</v>
+      </c>
+      <c r="K34" t="s">
+        <v>23</v>
+      </c>
+      <c r="L34" t="s">
+        <v>224</v>
+      </c>
+      <c r="M34" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>226</v>
+      </c>
+      <c r="B35" t="s">
+        <v>227</v>
+      </c>
+      <c r="C35" t="s">
+        <v>47</v>
+      </c>
+      <c r="D35" t="s">
+        <v>228</v>
+      </c>
+      <c r="E35" t="s">
+        <v>180</v>
+      </c>
+      <c r="F35" t="s">
+        <v>18</v>
+      </c>
+      <c r="G35" t="s">
+        <v>19</v>
+      </c>
+      <c r="H35" t="s">
+        <v>61</v>
+      </c>
+      <c r="I35" t="s">
+        <v>21</v>
+      </c>
+      <c r="J35" t="s">
+        <v>88</v>
+      </c>
+      <c r="K35" t="s">
+        <v>23</v>
+      </c>
+      <c r="L35" t="s">
+        <v>229</v>
+      </c>
+      <c r="M35" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>231</v>
+      </c>
+      <c r="B36" t="s">
+        <v>232</v>
+      </c>
+      <c r="C36" t="s">
+        <v>35</v>
+      </c>
+      <c r="D36" t="s">
+        <v>233</v>
+      </c>
+      <c r="E36" t="s">
+        <v>180</v>
+      </c>
+      <c r="F36" t="s">
+        <v>18</v>
+      </c>
+      <c r="G36" t="s">
+        <v>19</v>
+      </c>
+      <c r="H36" t="s">
+        <v>61</v>
+      </c>
+      <c r="I36" t="s">
+        <v>21</v>
+      </c>
+      <c r="J36" t="s">
+        <v>30</v>
+      </c>
+      <c r="K36" t="s">
+        <v>23</v>
+      </c>
+      <c r="L36" t="s">
+        <v>234</v>
+      </c>
+      <c r="M36" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>236</v>
+      </c>
+      <c r="B37" t="s">
+        <v>237</v>
+      </c>
+      <c r="C37" t="s">
+        <v>78</v>
+      </c>
+      <c r="D37" t="s">
+        <v>238</v>
+      </c>
+      <c r="E37" t="s">
+        <v>180</v>
+      </c>
+      <c r="F37" t="s">
+        <v>18</v>
+      </c>
+      <c r="G37" t="s">
+        <v>19</v>
+      </c>
+      <c r="H37" t="s">
+        <v>61</v>
+      </c>
+      <c r="I37" t="s">
+        <v>239</v>
+      </c>
+      <c r="J37" t="s">
+        <v>240</v>
+      </c>
+      <c r="K37" t="s">
+        <v>23</v>
+      </c>
+      <c r="L37" t="s">
+        <v>241</v>
+      </c>
+      <c r="M37" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>243</v>
+      </c>
+      <c r="B38" t="s">
+        <v>244</v>
+      </c>
+      <c r="C38" t="s">
+        <v>134</v>
+      </c>
+      <c r="D38" t="s">
+        <v>245</v>
+      </c>
+      <c r="E38" t="s">
+        <v>180</v>
+      </c>
+      <c r="F38" t="s">
+        <v>18</v>
+      </c>
+      <c r="G38" t="s">
+        <v>19</v>
+      </c>
+      <c r="H38" t="s">
+        <v>88</v>
+      </c>
+      <c r="I38" t="s">
+        <v>118</v>
+      </c>
+      <c r="J38" t="s">
+        <v>88</v>
+      </c>
+      <c r="K38" t="s">
+        <v>23</v>
+      </c>
+      <c r="L38" t="s">
+        <v>246</v>
+      </c>
+      <c r="M38" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>248</v>
+      </c>
+      <c r="B39" t="s">
+        <v>249</v>
+      </c>
+      <c r="C39" t="s">
+        <v>35</v>
+      </c>
+      <c r="D39" t="s">
+        <v>250</v>
+      </c>
+      <c r="E39" t="s">
+        <v>180</v>
+      </c>
+      <c r="F39" t="s">
+        <v>18</v>
+      </c>
+      <c r="G39" t="s">
+        <v>19</v>
+      </c>
+      <c r="H39" t="s">
+        <v>251</v>
+      </c>
+      <c r="I39" t="s">
+        <v>21</v>
+      </c>
+      <c r="J39" t="s">
+        <v>30</v>
+      </c>
+      <c r="K39" t="s">
+        <v>23</v>
+      </c>
+      <c r="L39" t="s">
+        <v>252</v>
+      </c>
+      <c r="M39" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>254</v>
+      </c>
+      <c r="B40" t="s">
+        <v>255</v>
+      </c>
+      <c r="C40" t="s">
+        <v>35</v>
+      </c>
+      <c r="D40" t="s">
+        <v>256</v>
+      </c>
+      <c r="E40" t="s">
+        <v>180</v>
+      </c>
+      <c r="F40" t="s">
+        <v>18</v>
+      </c>
+      <c r="G40" t="s">
+        <v>19</v>
+      </c>
+      <c r="H40" t="s">
+        <v>61</v>
+      </c>
+      <c r="I40" t="s">
+        <v>21</v>
+      </c>
+      <c r="J40" t="s">
+        <v>88</v>
+      </c>
+      <c r="K40" t="s">
+        <v>23</v>
+      </c>
+      <c r="L40" t="s">
+        <v>257</v>
+      </c>
+      <c r="M40" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>259</v>
+      </c>
+      <c r="B41" t="s">
+        <v>260</v>
+      </c>
+      <c r="C41" t="s">
+        <v>35</v>
+      </c>
+      <c r="D41" t="s">
+        <v>261</v>
+      </c>
+      <c r="E41" t="s">
+        <v>180</v>
+      </c>
+      <c r="F41" t="s">
+        <v>18</v>
+      </c>
+      <c r="G41" t="s">
+        <v>19</v>
+      </c>
+      <c r="H41" t="s">
+        <v>262</v>
+      </c>
+      <c r="I41" t="s">
+        <v>21</v>
+      </c>
+      <c r="J41" t="s">
+        <v>88</v>
+      </c>
+      <c r="K41" t="s">
+        <v>23</v>
+      </c>
+      <c r="L41" t="s">
+        <v>263</v>
+      </c>
+      <c r="M41" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>265</v>
+      </c>
+      <c r="B42" t="s">
+        <v>266</v>
+      </c>
+      <c r="C42" t="s">
+        <v>35</v>
+      </c>
+      <c r="D42" t="s">
+        <v>267</v>
+      </c>
+      <c r="E42" t="s">
+        <v>268</v>
+      </c>
+      <c r="F42" t="s">
+        <v>18</v>
+      </c>
+      <c r="G42" t="s">
+        <v>19</v>
+      </c>
+      <c r="H42" t="s">
+        <v>269</v>
+      </c>
+      <c r="I42" t="s">
+        <v>21</v>
+      </c>
+      <c r="J42" t="s">
+        <v>88</v>
+      </c>
+      <c r="K42" t="s">
+        <v>23</v>
+      </c>
+      <c r="L42" t="s">
+        <v>270</v>
+      </c>
+      <c r="M42" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>272</v>
+      </c>
+      <c r="B43" t="s">
+        <v>273</v>
+      </c>
+      <c r="C43" t="s">
+        <v>274</v>
+      </c>
+      <c r="D43" t="s">
+        <v>275</v>
+      </c>
+      <c r="E43" t="s">
+        <v>268</v>
+      </c>
+      <c r="F43" t="s">
+        <v>18</v>
+      </c>
+      <c r="G43" t="s">
+        <v>19</v>
+      </c>
+      <c r="H43" t="s">
+        <v>67</v>
+      </c>
+      <c r="I43" t="s">
+        <v>21</v>
+      </c>
+      <c r="J43" t="s">
+        <v>88</v>
+      </c>
+      <c r="K43" t="s">
+        <v>23</v>
+      </c>
+      <c r="L43" t="s">
+        <v>276</v>
+      </c>
+      <c r="M43" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>278</v>
+      </c>
+      <c r="B44" t="s">
+        <v>279</v>
+      </c>
+      <c r="C44" t="s">
+        <v>35</v>
+      </c>
+      <c r="D44" t="s">
+        <v>280</v>
+      </c>
+      <c r="E44" t="s">
+        <v>268</v>
+      </c>
+      <c r="F44" t="s">
+        <v>18</v>
+      </c>
+      <c r="G44" t="s">
+        <v>19</v>
+      </c>
+      <c r="H44" t="s">
+        <v>61</v>
+      </c>
+      <c r="I44" t="s">
+        <v>21</v>
+      </c>
+      <c r="J44" t="s">
+        <v>88</v>
+      </c>
+      <c r="K44" t="s">
+        <v>23</v>
+      </c>
+      <c r="L44" t="s">
+        <v>281</v>
+      </c>
+      <c r="M44" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>283</v>
+      </c>
+      <c r="B45" t="s">
+        <v>284</v>
+      </c>
+      <c r="C45" t="s">
+        <v>35</v>
+      </c>
+      <c r="D45" t="s">
+        <v>285</v>
+      </c>
+      <c r="E45" t="s">
+        <v>268</v>
+      </c>
+      <c r="F45" t="s">
+        <v>18</v>
+      </c>
+      <c r="G45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H45" t="s">
+        <v>61</v>
+      </c>
+      <c r="I45" t="s">
+        <v>21</v>
+      </c>
+      <c r="J45" t="s">
+        <v>30</v>
+      </c>
+      <c r="K45" t="s">
+        <v>23</v>
+      </c>
+      <c r="L45" t="s">
+        <v>286</v>
+      </c>
+      <c r="M45" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>288</v>
+      </c>
+      <c r="B46" t="s">
+        <v>289</v>
+      </c>
+      <c r="C46" t="s">
+        <v>35</v>
+      </c>
+      <c r="D46" t="s">
+        <v>290</v>
+      </c>
+      <c r="E46" t="s">
+        <v>268</v>
+      </c>
+      <c r="F46" t="s">
+        <v>18</v>
+      </c>
+      <c r="G46" t="s">
+        <v>19</v>
+      </c>
+      <c r="H46" t="s">
+        <v>29</v>
+      </c>
+      <c r="I46" t="s">
+        <v>21</v>
+      </c>
+      <c r="J46" t="s">
+        <v>30</v>
+      </c>
+      <c r="K46" t="s">
+        <v>23</v>
+      </c>
+      <c r="L46" t="s">
+        <v>291</v>
+      </c>
+      <c r="M46" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>293</v>
+      </c>
+      <c r="B47" t="s">
+        <v>294</v>
+      </c>
+      <c r="C47" t="s">
+        <v>35</v>
+      </c>
+      <c r="D47" t="s">
+        <v>295</v>
+      </c>
+      <c r="E47" t="s">
+        <v>268</v>
+      </c>
+      <c r="F47" t="s">
+        <v>18</v>
+      </c>
+      <c r="G47" t="s">
+        <v>19</v>
+      </c>
+      <c r="H47" t="s">
+        <v>49</v>
+      </c>
+      <c r="I47" t="s">
+        <v>21</v>
+      </c>
+      <c r="J47" t="s">
+        <v>88</v>
+      </c>
+      <c r="K47" t="s">
+        <v>23</v>
+      </c>
+      <c r="L47" t="s">
+        <v>296</v>
+      </c>
+      <c r="M47" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>298</v>
+      </c>
+      <c r="B48" t="s">
+        <v>299</v>
+      </c>
+      <c r="C48" t="s">
+        <v>35</v>
+      </c>
+      <c r="D48" t="s">
+        <v>300</v>
+      </c>
+      <c r="E48" t="s">
+        <v>268</v>
+      </c>
+      <c r="F48" t="s">
+        <v>18</v>
+      </c>
+      <c r="G48" t="s">
+        <v>19</v>
+      </c>
+      <c r="H48" t="s">
+        <v>61</v>
+      </c>
+      <c r="I48" t="s">
+        <v>21</v>
+      </c>
+      <c r="J48" t="s">
+        <v>88</v>
+      </c>
+      <c r="K48" t="s">
+        <v>23</v>
+      </c>
+      <c r="L48" t="s">
+        <v>301</v>
+      </c>
+      <c r="M48" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>303</v>
+      </c>
+      <c r="B49" t="s">
+        <v>304</v>
+      </c>
+      <c r="C49" t="s">
+        <v>35</v>
+      </c>
+      <c r="D49" t="s">
+        <v>305</v>
+      </c>
+      <c r="E49" t="s">
+        <v>268</v>
+      </c>
+      <c r="F49" t="s">
+        <v>18</v>
+      </c>
+      <c r="G49" t="s">
+        <v>19</v>
+      </c>
+      <c r="H49" t="s">
+        <v>61</v>
+      </c>
+      <c r="I49" t="s">
+        <v>21</v>
+      </c>
+      <c r="J49" t="s">
+        <v>30</v>
+      </c>
+      <c r="K49" t="s">
+        <v>23</v>
+      </c>
+      <c r="L49" t="s">
+        <v>306</v>
+      </c>
+      <c r="M49" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>308</v>
+      </c>
+      <c r="B50" t="s">
+        <v>309</v>
+      </c>
+      <c r="C50" t="s">
+        <v>134</v>
+      </c>
+      <c r="D50" t="s">
+        <v>310</v>
+      </c>
+      <c r="E50" t="s">
+        <v>268</v>
+      </c>
+      <c r="F50" t="s">
+        <v>18</v>
+      </c>
+      <c r="G50" t="s">
+        <v>19</v>
+      </c>
+      <c r="H50" t="s">
+        <v>88</v>
+      </c>
+      <c r="I50" t="s">
+        <v>118</v>
+      </c>
+      <c r="J50" t="s">
+        <v>88</v>
+      </c>
+      <c r="K50" t="s">
+        <v>23</v>
+      </c>
+      <c r="L50" t="s">
+        <v>311</v>
+      </c>
+      <c r="M50" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>313</v>
+      </c>
+      <c r="B51" t="s">
+        <v>314</v>
+      </c>
+      <c r="C51" t="s">
+        <v>315</v>
+      </c>
+      <c r="D51" t="s">
+        <v>316</v>
+      </c>
+      <c r="E51" t="s">
+        <v>268</v>
+      </c>
+      <c r="F51" t="s">
+        <v>18</v>
+      </c>
+      <c r="G51" t="s">
+        <v>19</v>
+      </c>
+      <c r="H51" t="s">
+        <v>61</v>
+      </c>
+      <c r="I51" t="s">
+        <v>317</v>
+      </c>
+      <c r="J51" t="s">
+        <v>318</v>
+      </c>
+      <c r="K51" t="s">
+        <v>23</v>
+      </c>
+      <c r="L51" t="s">
+        <v>319</v>
+      </c>
+      <c r="M51" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>321</v>
+      </c>
+      <c r="B52" t="s">
+        <v>322</v>
+      </c>
+      <c r="C52" t="s">
+        <v>35</v>
+      </c>
+      <c r="D52" t="s">
+        <v>323</v>
+      </c>
+      <c r="E52" t="s">
+        <v>268</v>
+      </c>
+      <c r="F52" t="s">
+        <v>18</v>
+      </c>
+      <c r="G52" t="s">
+        <v>19</v>
+      </c>
+      <c r="H52" t="s">
+        <v>61</v>
+      </c>
+      <c r="I52" t="s">
+        <v>21</v>
+      </c>
+      <c r="J52" t="s">
+        <v>88</v>
+      </c>
+      <c r="K52" t="s">
+        <v>23</v>
+      </c>
+      <c r="L52" t="s">
+        <v>324</v>
+      </c>
+      <c r="M52" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>326</v>
+      </c>
+      <c r="B53" t="s">
+        <v>327</v>
+      </c>
+      <c r="C53" t="s">
+        <v>35</v>
+      </c>
+      <c r="D53" t="s">
+        <v>328</v>
+      </c>
+      <c r="E53" t="s">
+        <v>268</v>
+      </c>
+      <c r="F53" t="s">
+        <v>18</v>
+      </c>
+      <c r="G53" t="s">
+        <v>19</v>
+      </c>
+      <c r="H53" t="s">
+        <v>61</v>
+      </c>
+      <c r="I53" t="s">
+        <v>21</v>
+      </c>
+      <c r="J53" t="s">
+        <v>88</v>
+      </c>
+      <c r="K53" t="s">
+        <v>23</v>
+      </c>
+      <c r="L53" t="s">
+        <v>329</v>
+      </c>
+      <c r="M53" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>331</v>
+      </c>
+      <c r="B54" t="s">
+        <v>332</v>
+      </c>
+      <c r="C54" t="s">
+        <v>35</v>
+      </c>
+      <c r="D54" t="s">
+        <v>333</v>
+      </c>
+      <c r="E54" t="s">
+        <v>268</v>
+      </c>
+      <c r="F54" t="s">
+        <v>18</v>
+      </c>
+      <c r="G54" t="s">
+        <v>19</v>
+      </c>
+      <c r="H54" t="s">
+        <v>61</v>
+      </c>
+      <c r="I54" t="s">
+        <v>21</v>
+      </c>
+      <c r="J54" t="s">
+        <v>88</v>
+      </c>
+      <c r="K54" t="s">
+        <v>23</v>
+      </c>
+      <c r="L54" t="s">
+        <v>334</v>
+      </c>
+      <c r="M54" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>336</v>
+      </c>
+      <c r="B55" t="s">
+        <v>337</v>
+      </c>
+      <c r="C55" t="s">
+        <v>35</v>
+      </c>
+      <c r="D55" t="s">
+        <v>338</v>
+      </c>
+      <c r="E55" t="s">
+        <v>268</v>
+      </c>
+      <c r="F55" t="s">
+        <v>18</v>
+      </c>
+      <c r="G55" t="s">
+        <v>19</v>
+      </c>
+      <c r="H55" t="s">
+        <v>88</v>
+      </c>
+      <c r="I55" t="s">
+        <v>118</v>
+      </c>
+      <c r="J55" t="s">
+        <v>88</v>
+      </c>
+      <c r="K55" t="s">
+        <v>23</v>
+      </c>
+      <c r="L55" t="s">
+        <v>339</v>
+      </c>
+      <c r="M55" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>341</v>
+      </c>
+      <c r="B56" t="s">
+        <v>342</v>
+      </c>
+      <c r="C56" t="s">
+        <v>47</v>
+      </c>
+      <c r="D56" t="s">
+        <v>343</v>
+      </c>
+      <c r="E56" t="s">
+        <v>268</v>
+      </c>
+      <c r="F56" t="s">
+        <v>18</v>
+      </c>
+      <c r="G56" t="s">
+        <v>19</v>
+      </c>
+      <c r="H56" t="s">
+        <v>344</v>
+      </c>
+      <c r="I56" t="s">
+        <v>21</v>
+      </c>
+      <c r="J56" t="s">
+        <v>88</v>
+      </c>
+      <c r="K56" t="s">
+        <v>23</v>
+      </c>
+      <c r="L56" t="s">
+        <v>345</v>
+      </c>
+      <c r="M56" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>347</v>
+      </c>
+      <c r="B57" t="s">
+        <v>348</v>
+      </c>
+      <c r="C57" t="s">
+        <v>35</v>
+      </c>
+      <c r="D57" t="s">
+        <v>349</v>
+      </c>
+      <c r="E57" t="s">
+        <v>268</v>
+      </c>
+      <c r="F57" t="s">
+        <v>18</v>
+      </c>
+      <c r="G57" t="s">
+        <v>19</v>
+      </c>
+      <c r="H57" t="s">
+        <v>61</v>
+      </c>
+      <c r="I57" t="s">
+        <v>21</v>
+      </c>
+      <c r="J57" t="s">
+        <v>30</v>
+      </c>
+      <c r="K57" t="s">
+        <v>23</v>
+      </c>
+      <c r="L57" t="s">
+        <v>350</v>
+      </c>
+      <c r="M57" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>352</v>
+      </c>
+      <c r="B58" t="s">
+        <v>353</v>
+      </c>
+      <c r="C58" t="s">
+        <v>35</v>
+      </c>
+      <c r="D58" t="s">
+        <v>354</v>
+      </c>
+      <c r="E58" t="s">
+        <v>268</v>
+      </c>
+      <c r="F58" t="s">
+        <v>18</v>
+      </c>
+      <c r="G58" t="s">
+        <v>19</v>
+      </c>
+      <c r="H58" t="s">
+        <v>88</v>
+      </c>
+      <c r="I58" t="s">
+        <v>118</v>
+      </c>
+      <c r="J58" t="s">
+        <v>50</v>
+      </c>
+      <c r="K58" t="s">
+        <v>23</v>
+      </c>
+      <c r="L58" t="s">
+        <v>355</v>
+      </c>
+      <c r="M58" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>357</v>
+      </c>
+      <c r="B59" t="s">
+        <v>358</v>
+      </c>
+      <c r="C59" t="s">
+        <v>35</v>
+      </c>
+      <c r="D59" t="s">
+        <v>359</v>
+      </c>
+      <c r="E59" t="s">
+        <v>268</v>
+      </c>
+      <c r="F59" t="s">
+        <v>18</v>
+      </c>
+      <c r="G59" t="s">
+        <v>19</v>
+      </c>
+      <c r="H59" t="s">
+        <v>88</v>
+      </c>
+      <c r="I59" t="s">
+        <v>118</v>
+      </c>
+      <c r="J59" t="s">
+        <v>88</v>
+      </c>
+      <c r="K59" t="s">
+        <v>23</v>
+      </c>
+      <c r="L59" t="s">
+        <v>360</v>
+      </c>
+      <c r="M59" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>362</v>
+      </c>
+      <c r="B60" t="s">
+        <v>363</v>
+      </c>
+      <c r="C60" t="s">
+        <v>35</v>
+      </c>
+      <c r="D60" t="s">
+        <v>364</v>
+      </c>
+      <c r="E60" t="s">
+        <v>268</v>
+      </c>
+      <c r="F60" t="s">
+        <v>18</v>
+      </c>
+      <c r="G60" t="s">
+        <v>19</v>
+      </c>
+      <c r="H60" t="s">
+        <v>61</v>
+      </c>
+      <c r="I60" t="s">
+        <v>21</v>
+      </c>
+      <c r="J60" t="s">
+        <v>88</v>
+      </c>
+      <c r="K60" t="s">
+        <v>23</v>
+      </c>
+      <c r="L60" t="s">
+        <v>365</v>
+      </c>
+      <c r="M60" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>367</v>
+      </c>
+      <c r="B61" t="s">
+        <v>368</v>
+      </c>
+      <c r="C61" t="s">
+        <v>369</v>
+      </c>
+      <c r="D61" t="s">
+        <v>370</v>
+      </c>
+      <c r="E61" t="s">
+        <v>268</v>
+      </c>
+      <c r="F61" t="s">
+        <v>18</v>
+      </c>
+      <c r="G61" t="s">
+        <v>19</v>
+      </c>
+      <c r="H61" t="s">
+        <v>344</v>
+      </c>
+      <c r="I61" t="s">
+        <v>21</v>
+      </c>
+      <c r="J61" t="s">
+        <v>30</v>
+      </c>
+      <c r="K61" t="s">
+        <v>23</v>
+      </c>
+      <c r="L61" t="s">
+        <v>371</v>
+      </c>
+      <c r="M61" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>373</v>
+      </c>
+      <c r="B62" t="s">
+        <v>374</v>
+      </c>
+      <c r="C62" t="s">
+        <v>35</v>
+      </c>
+      <c r="D62" t="s">
+        <v>375</v>
+      </c>
+      <c r="E62" t="s">
+        <v>268</v>
+      </c>
+      <c r="F62" t="s">
+        <v>18</v>
+      </c>
+      <c r="G62" t="s">
+        <v>19</v>
+      </c>
+      <c r="H62" t="s">
+        <v>88</v>
+      </c>
+      <c r="I62" t="s">
+        <v>118</v>
+      </c>
+      <c r="J62" t="s">
+        <v>30</v>
+      </c>
+      <c r="K62" t="s">
+        <v>23</v>
+      </c>
+      <c r="L62" t="s">
+        <v>376</v>
+      </c>
+      <c r="M62" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>378</v>
+      </c>
+      <c r="B63" t="s">
+        <v>379</v>
+      </c>
+      <c r="C63" t="s">
+        <v>35</v>
+      </c>
+      <c r="D63" t="s">
+        <v>380</v>
+      </c>
+      <c r="E63" t="s">
+        <v>268</v>
+      </c>
+      <c r="F63" t="s">
+        <v>18</v>
+      </c>
+      <c r="G63" t="s">
+        <v>19</v>
+      </c>
+      <c r="H63" t="s">
+        <v>61</v>
+      </c>
+      <c r="I63" t="s">
+        <v>21</v>
+      </c>
+      <c r="J63" t="s">
+        <v>88</v>
+      </c>
+      <c r="K63" t="s">
+        <v>23</v>
+      </c>
+      <c r="L63" t="s">
+        <v>381</v>
+      </c>
+      <c r="M63" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>383</v>
+      </c>
+      <c r="B64" t="s">
+        <v>384</v>
+      </c>
+      <c r="C64" t="s">
+        <v>35</v>
+      </c>
+      <c r="D64" t="s">
+        <v>385</v>
+      </c>
+      <c r="E64" t="s">
+        <v>268</v>
+      </c>
+      <c r="F64" t="s">
+        <v>18</v>
+      </c>
+      <c r="G64" t="s">
+        <v>19</v>
+      </c>
+      <c r="H64" t="s">
+        <v>61</v>
+      </c>
+      <c r="I64" t="s">
+        <v>21</v>
+      </c>
+      <c r="J64" t="s">
+        <v>88</v>
+      </c>
+      <c r="K64" t="s">
+        <v>23</v>
+      </c>
+      <c r="L64" t="s">
+        <v>386</v>
+      </c>
+      <c r="M64" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>388</v>
+      </c>
+      <c r="B65" t="s">
+        <v>389</v>
+      </c>
+      <c r="C65" t="s">
+        <v>390</v>
+      </c>
+      <c r="D65" t="s">
+        <v>391</v>
+      </c>
+      <c r="E65" t="s">
+        <v>268</v>
+      </c>
+      <c r="F65" t="s">
+        <v>18</v>
+      </c>
+      <c r="G65" t="s">
+        <v>19</v>
+      </c>
+      <c r="H65" t="s">
+        <v>88</v>
+      </c>
+      <c r="I65" t="s">
+        <v>118</v>
+      </c>
+      <c r="J65" t="s">
+        <v>88</v>
+      </c>
+      <c r="K65" t="s">
+        <v>23</v>
+      </c>
+      <c r="L65" t="s">
+        <v>392</v>
+      </c>
+      <c r="M65" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>394</v>
+      </c>
+      <c r="B66" t="s">
+        <v>395</v>
+      </c>
+      <c r="C66" t="s">
+        <v>35</v>
+      </c>
+      <c r="D66" t="s">
+        <v>396</v>
+      </c>
+      <c r="E66" t="s">
+        <v>268</v>
+      </c>
+      <c r="F66" t="s">
+        <v>18</v>
+      </c>
+      <c r="G66" t="s">
+        <v>19</v>
+      </c>
+      <c r="H66" t="s">
+        <v>61</v>
+      </c>
+      <c r="I66" t="s">
+        <v>21</v>
+      </c>
+      <c r="J66" t="s">
+        <v>30</v>
+      </c>
+      <c r="K66" t="s">
+        <v>23</v>
+      </c>
+      <c r="L66" t="s">
+        <v>397</v>
+      </c>
+      <c r="M66" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>399</v>
+      </c>
+      <c r="B67" t="s">
+        <v>400</v>
+      </c>
+      <c r="C67" t="s">
+        <v>35</v>
+      </c>
+      <c r="D67" t="s">
+        <v>401</v>
+      </c>
+      <c r="E67" t="s">
+        <v>268</v>
+      </c>
+      <c r="F67" t="s">
+        <v>18</v>
+      </c>
+      <c r="G67" t="s">
+        <v>19</v>
+      </c>
+      <c r="H67" t="s">
+        <v>88</v>
+      </c>
+      <c r="I67" t="s">
+        <v>118</v>
+      </c>
+      <c r="J67" t="s">
+        <v>88</v>
+      </c>
+      <c r="K67" t="s">
+        <v>23</v>
+      </c>
+      <c r="L67" t="s">
+        <v>402</v>
+      </c>
+      <c r="M67" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>404</v>
+      </c>
+      <c r="B68" t="s">
+        <v>405</v>
+      </c>
+      <c r="C68" t="s">
+        <v>35</v>
+      </c>
+      <c r="D68" t="s">
+        <v>406</v>
+      </c>
+      <c r="E68" t="s">
+        <v>268</v>
+      </c>
+      <c r="F68" t="s">
+        <v>18</v>
+      </c>
+      <c r="G68" t="s">
+        <v>19</v>
+      </c>
+      <c r="H68" t="s">
+        <v>61</v>
+      </c>
+      <c r="I68" t="s">
+        <v>21</v>
+      </c>
+      <c r="J68" t="s">
+        <v>88</v>
+      </c>
+      <c r="K68" t="s">
+        <v>23</v>
+      </c>
+      <c r="L68" t="s">
+        <v>407</v>
+      </c>
+      <c r="M68" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>409</v>
+      </c>
+      <c r="B69" t="s">
+        <v>410</v>
+      </c>
+      <c r="C69" t="s">
+        <v>15</v>
+      </c>
+      <c r="D69" t="s">
+        <v>411</v>
+      </c>
+      <c r="E69" t="s">
+        <v>412</v>
+      </c>
+      <c r="F69" t="s">
+        <v>18</v>
+      </c>
+      <c r="G69" t="s">
+        <v>19</v>
+      </c>
+      <c r="H69" t="s">
+        <v>20</v>
+      </c>
+      <c r="I69" t="s">
+        <v>21</v>
+      </c>
+      <c r="J69" t="s">
+        <v>50</v>
+      </c>
+      <c r="K69" t="s">
+        <v>23</v>
+      </c>
+      <c r="L69" t="s">
+        <v>413</v>
+      </c>
+      <c r="M69" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>415</v>
+      </c>
+      <c r="B70" t="s">
+        <v>416</v>
+      </c>
+      <c r="C70" t="s">
+        <v>15</v>
+      </c>
+      <c r="D70" t="s">
+        <v>417</v>
+      </c>
+      <c r="E70" t="s">
+        <v>412</v>
+      </c>
+      <c r="F70" t="s">
+        <v>18</v>
+      </c>
+      <c r="G70" t="s">
+        <v>19</v>
+      </c>
+      <c r="H70" t="s">
+        <v>418</v>
+      </c>
+      <c r="I70" t="s">
+        <v>21</v>
+      </c>
+      <c r="J70" t="s">
+        <v>30</v>
+      </c>
+      <c r="K70" t="s">
+        <v>23</v>
+      </c>
+      <c r="L70" t="s">
+        <v>419</v>
+      </c>
+      <c r="M70" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>421</v>
+      </c>
+      <c r="B71" t="s">
+        <v>422</v>
+      </c>
+      <c r="C71" t="s">
+        <v>35</v>
+      </c>
+      <c r="D71" t="s">
+        <v>423</v>
+      </c>
+      <c r="E71" t="s">
+        <v>412</v>
+      </c>
+      <c r="F71" t="s">
+        <v>18</v>
+      </c>
+      <c r="G71" t="s">
+        <v>19</v>
+      </c>
+      <c r="H71" t="s">
+        <v>223</v>
+      </c>
+      <c r="I71" t="s">
+        <v>21</v>
+      </c>
+      <c r="J71" t="s">
+        <v>22</v>
+      </c>
+      <c r="K71" t="s">
+        <v>23</v>
+      </c>
+      <c r="L71" t="s">
+        <v>424</v>
+      </c>
+      <c r="M71" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>426</v>
+      </c>
+      <c r="B72" t="s">
+        <v>427</v>
+      </c>
+      <c r="C72" t="s">
+        <v>35</v>
+      </c>
+      <c r="D72" t="s">
+        <v>428</v>
+      </c>
+      <c r="E72" t="s">
+        <v>412</v>
+      </c>
+      <c r="F72" t="s">
+        <v>18</v>
+      </c>
+      <c r="G72" t="s">
+        <v>19</v>
+      </c>
+      <c r="H72" t="s">
+        <v>61</v>
+      </c>
+      <c r="I72" t="s">
+        <v>21</v>
+      </c>
+      <c r="J72" t="s">
+        <v>30</v>
+      </c>
+      <c r="K72" t="s">
+        <v>23</v>
+      </c>
+      <c r="L72" t="s">
+        <v>429</v>
+      </c>
+      <c r="M72" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>431</v>
+      </c>
+      <c r="B73" t="s">
+        <v>432</v>
+      </c>
+      <c r="C73" t="s">
+        <v>35</v>
+      </c>
+      <c r="D73" t="s">
+        <v>433</v>
+      </c>
+      <c r="E73" t="s">
+        <v>412</v>
+      </c>
+      <c r="F73" t="s">
+        <v>18</v>
+      </c>
+      <c r="G73" t="s">
+        <v>19</v>
+      </c>
+      <c r="H73" t="s">
+        <v>166</v>
+      </c>
+      <c r="I73" t="s">
+        <v>21</v>
+      </c>
+      <c r="J73" t="s">
+        <v>30</v>
+      </c>
+      <c r="K73" t="s">
+        <v>23</v>
+      </c>
+      <c r="L73" t="s">
+        <v>434</v>
+      </c>
+      <c r="M73" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>436</v>
+      </c>
+      <c r="B74" t="s">
+        <v>437</v>
+      </c>
+      <c r="C74" t="s">
+        <v>35</v>
+      </c>
+      <c r="D74" t="s">
+        <v>438</v>
+      </c>
+      <c r="E74" t="s">
+        <v>412</v>
+      </c>
+      <c r="F74" t="s">
+        <v>18</v>
+      </c>
+      <c r="G74" t="s">
+        <v>19</v>
+      </c>
+      <c r="H74" t="s">
+        <v>193</v>
+      </c>
+      <c r="I74" t="s">
+        <v>21</v>
+      </c>
+      <c r="J74" t="s">
+        <v>88</v>
+      </c>
+      <c r="K74" t="s">
+        <v>23</v>
+      </c>
+      <c r="L74" t="s">
+        <v>439</v>
+      </c>
+      <c r="M74" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>441</v>
+      </c>
+      <c r="B75" t="s">
+        <v>442</v>
+      </c>
+      <c r="C75" t="s">
+        <v>35</v>
+      </c>
+      <c r="D75" t="s">
+        <v>443</v>
+      </c>
+      <c r="E75" t="s">
+        <v>412</v>
+      </c>
+      <c r="F75" t="s">
+        <v>18</v>
+      </c>
+      <c r="G75" t="s">
+        <v>19</v>
+      </c>
+      <c r="H75" t="s">
+        <v>88</v>
+      </c>
+      <c r="I75" t="s">
+        <v>118</v>
+      </c>
+      <c r="J75" t="s">
+        <v>88</v>
+      </c>
+      <c r="K75" t="s">
+        <v>23</v>
+      </c>
+      <c r="L75" t="s">
+        <v>444</v>
+      </c>
+      <c r="M75" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>446</v>
+      </c>
+      <c r="B76" t="s">
+        <v>447</v>
+      </c>
+      <c r="C76" t="s">
+        <v>35</v>
+      </c>
+      <c r="D76" t="s">
+        <v>448</v>
+      </c>
+      <c r="E76" t="s">
+        <v>449</v>
+      </c>
+      <c r="F76" t="s">
+        <v>18</v>
+      </c>
+      <c r="G76" t="s">
+        <v>19</v>
+      </c>
+      <c r="H76" t="s">
+        <v>223</v>
+      </c>
+      <c r="I76" t="s">
+        <v>21</v>
+      </c>
+      <c r="J76" t="s">
+        <v>88</v>
+      </c>
+      <c r="K76" t="s">
+        <v>23</v>
+      </c>
+      <c r="L76" t="s">
+        <v>450</v>
+      </c>
+      <c r="M76" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>452</v>
+      </c>
+      <c r="B77" t="s">
+        <v>453</v>
+      </c>
+      <c r="C77" t="s">
+        <v>35</v>
+      </c>
+      <c r="D77" t="s">
+        <v>454</v>
+      </c>
+      <c r="E77" t="s">
+        <v>455</v>
+      </c>
+      <c r="F77" t="s">
+        <v>18</v>
+      </c>
+      <c r="G77" t="s">
+        <v>19</v>
+      </c>
+      <c r="H77" t="s">
+        <v>61</v>
+      </c>
+      <c r="I77" t="s">
+        <v>21</v>
+      </c>
+      <c r="J77" t="s">
+        <v>30</v>
+      </c>
+      <c r="K77" t="s">
+        <v>23</v>
+      </c>
+      <c r="L77" t="s">
+        <v>456</v>
+      </c>
+      <c r="M77" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>458</v>
+      </c>
+      <c r="B78" t="s">
+        <v>459</v>
+      </c>
+      <c r="C78" t="s">
+        <v>35</v>
+      </c>
+      <c r="D78" t="s">
+        <v>460</v>
+      </c>
+      <c r="E78" t="s">
+        <v>461</v>
+      </c>
+      <c r="F78" t="s">
+        <v>18</v>
+      </c>
+      <c r="G78" t="s">
+        <v>19</v>
+      </c>
+      <c r="H78" t="s">
+        <v>37</v>
+      </c>
+      <c r="I78" t="s">
+        <v>21</v>
+      </c>
+      <c r="J78" t="s">
+        <v>30</v>
+      </c>
+      <c r="K78" t="s">
+        <v>23</v>
+      </c>
+      <c r="L78" t="s">
+        <v>462</v>
+      </c>
+      <c r="M78" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>464</v>
+      </c>
+      <c r="B79" t="s">
+        <v>465</v>
+      </c>
+      <c r="C79" t="s">
+        <v>35</v>
+      </c>
+      <c r="D79" t="s">
+        <v>466</v>
+      </c>
+      <c r="E79" t="s">
+        <v>467</v>
+      </c>
+      <c r="F79" t="s">
+        <v>18</v>
+      </c>
+      <c r="G79" t="s">
+        <v>19</v>
+      </c>
+      <c r="H79" t="s">
+        <v>88</v>
+      </c>
+      <c r="I79" t="s">
+        <v>118</v>
+      </c>
+      <c r="J79" t="s">
+        <v>88</v>
+      </c>
+      <c r="K79" t="s">
+        <v>23</v>
+      </c>
+      <c r="L79" t="s">
+        <v>468</v>
+      </c>
+      <c r="M79" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>470</v>
+      </c>
+      <c r="B80" t="s">
+        <v>471</v>
+      </c>
+      <c r="C80" t="s">
+        <v>35</v>
+      </c>
+      <c r="D80" t="s">
+        <v>472</v>
+      </c>
+      <c r="E80" t="s">
+        <v>412</v>
+      </c>
+      <c r="F80" t="s">
+        <v>18</v>
+      </c>
+      <c r="G80" t="s">
+        <v>19</v>
+      </c>
+      <c r="H80" t="s">
+        <v>61</v>
+      </c>
+      <c r="I80" t="s">
+        <v>21</v>
+      </c>
+      <c r="J80" t="s">
+        <v>88</v>
+      </c>
+      <c r="K80" t="s">
+        <v>23</v>
+      </c>
+      <c r="L80" t="s">
+        <v>473</v>
+      </c>
+      <c r="M80" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>475</v>
+      </c>
+      <c r="B81" t="s">
+        <v>476</v>
+      </c>
+      <c r="C81" t="s">
+        <v>35</v>
+      </c>
+      <c r="D81" t="s">
+        <v>477</v>
+      </c>
+      <c r="E81" t="s">
+        <v>478</v>
+      </c>
+      <c r="F81" t="s">
+        <v>18</v>
+      </c>
+      <c r="G81" t="s">
+        <v>19</v>
+      </c>
+      <c r="H81" t="s">
+        <v>61</v>
+      </c>
+      <c r="I81" t="s">
+        <v>21</v>
+      </c>
+      <c r="J81" t="s">
+        <v>30</v>
+      </c>
+      <c r="K81" t="s">
+        <v>23</v>
+      </c>
+      <c r="L81" t="s">
+        <v>479</v>
+      </c>
+      <c r="M81" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>481</v>
+      </c>
+      <c r="B82" t="s">
+        <v>482</v>
+      </c>
+      <c r="C82" t="s">
+        <v>483</v>
+      </c>
+      <c r="D82" t="s">
+        <v>484</v>
+      </c>
+      <c r="E82" t="s">
+        <v>412</v>
+      </c>
+      <c r="F82" t="s">
+        <v>18</v>
+      </c>
+      <c r="G82" t="s">
+        <v>19</v>
+      </c>
+      <c r="H82" t="s">
+        <v>61</v>
+      </c>
+      <c r="I82" t="s">
+        <v>485</v>
+      </c>
+      <c r="J82" t="s">
+        <v>88</v>
+      </c>
+      <c r="K82" t="s">
+        <v>23</v>
+      </c>
+      <c r="L82" t="s">
+        <v>486</v>
+      </c>
+      <c r="M82" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>488</v>
+      </c>
+      <c r="B83" t="s">
+        <v>489</v>
+      </c>
+      <c r="C83" t="s">
+        <v>78</v>
+      </c>
+      <c r="D83" t="s">
+        <v>490</v>
+      </c>
+      <c r="E83" t="s">
+        <v>412</v>
+      </c>
+      <c r="F83" t="s">
+        <v>18</v>
+      </c>
+      <c r="G83" t="s">
+        <v>19</v>
+      </c>
+      <c r="H83" t="s">
+        <v>88</v>
+      </c>
+      <c r="I83" t="s">
+        <v>239</v>
+      </c>
+      <c r="J83" t="s">
+        <v>88</v>
+      </c>
+      <c r="K83" t="s">
+        <v>23</v>
+      </c>
+      <c r="L83" t="s">
+        <v>491</v>
+      </c>
+      <c r="M83" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>493</v>
+      </c>
+      <c r="B84" t="s">
+        <v>494</v>
+      </c>
+      <c r="C84" t="s">
+        <v>274</v>
+      </c>
+      <c r="D84" t="s">
+        <v>495</v>
+      </c>
+      <c r="E84" t="s">
+        <v>496</v>
+      </c>
+      <c r="F84" t="s">
+        <v>18</v>
+      </c>
+      <c r="G84" t="s">
+        <v>19</v>
+      </c>
+      <c r="H84" t="s">
+        <v>61</v>
+      </c>
+      <c r="I84" t="s">
+        <v>21</v>
+      </c>
+      <c r="J84" t="s">
+        <v>88</v>
+      </c>
+      <c r="K84" t="s">
+        <v>23</v>
+      </c>
+      <c r="L84" t="s">
+        <v>497</v>
+      </c>
+      <c r="M84" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>499</v>
+      </c>
+      <c r="B85" t="s">
+        <v>500</v>
+      </c>
+      <c r="C85" t="s">
+        <v>35</v>
+      </c>
+      <c r="D85" t="s">
+        <v>501</v>
+      </c>
+      <c r="E85" t="s">
+        <v>496</v>
+      </c>
+      <c r="F85" t="s">
+        <v>18</v>
+      </c>
+      <c r="G85" t="s">
+        <v>19</v>
+      </c>
+      <c r="H85" t="s">
+        <v>20</v>
+      </c>
+      <c r="I85" t="s">
+        <v>21</v>
+      </c>
+      <c r="J85" t="s">
+        <v>88</v>
+      </c>
+      <c r="K85" t="s">
+        <v>23</v>
+      </c>
+      <c r="L85" t="s">
+        <v>502</v>
+      </c>
+      <c r="M85" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>504</v>
+      </c>
+      <c r="B86" t="s">
+        <v>505</v>
+      </c>
+      <c r="C86" t="s">
+        <v>35</v>
+      </c>
+      <c r="D86" t="s">
+        <v>506</v>
+      </c>
+      <c r="E86" t="s">
+        <v>412</v>
+      </c>
+      <c r="F86" t="s">
+        <v>18</v>
+      </c>
+      <c r="G86" t="s">
+        <v>19</v>
+      </c>
+      <c r="H86" t="s">
+        <v>88</v>
+      </c>
+      <c r="I86" t="s">
+        <v>118</v>
+      </c>
+      <c r="J86" t="s">
+        <v>88</v>
+      </c>
+      <c r="K86" t="s">
+        <v>23</v>
+      </c>
+      <c r="L86" t="s">
+        <v>507</v>
+      </c>
+      <c r="M86" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>509</v>
+      </c>
+      <c r="B87" t="s">
+        <v>510</v>
+      </c>
+      <c r="C87" t="s">
+        <v>35</v>
+      </c>
+      <c r="D87" t="s">
+        <v>511</v>
+      </c>
+      <c r="E87" t="s">
+        <v>412</v>
+      </c>
+      <c r="F87" t="s">
+        <v>18</v>
+      </c>
+      <c r="G87" t="s">
+        <v>19</v>
+      </c>
+      <c r="H87" t="s">
+        <v>20</v>
+      </c>
+      <c r="I87" t="s">
+        <v>21</v>
+      </c>
+      <c r="J87" t="s">
+        <v>88</v>
+      </c>
+      <c r="K87" t="s">
+        <v>23</v>
+      </c>
+      <c r="L87" t="s">
+        <v>512</v>
+      </c>
+      <c r="M87" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>514</v>
+      </c>
+      <c r="B88" t="s">
+        <v>515</v>
+      </c>
+      <c r="C88" t="s">
+        <v>35</v>
+      </c>
+      <c r="D88" t="s">
+        <v>516</v>
+      </c>
+      <c r="E88" t="s">
+        <v>412</v>
+      </c>
+      <c r="F88" t="s">
+        <v>18</v>
+      </c>
+      <c r="G88" t="s">
+        <v>19</v>
+      </c>
+      <c r="H88" t="s">
+        <v>88</v>
+      </c>
+      <c r="I88" t="s">
+        <v>118</v>
+      </c>
+      <c r="J88" t="s">
+        <v>88</v>
+      </c>
+      <c r="K88" t="s">
+        <v>23</v>
+      </c>
+      <c r="L88" t="s">
+        <v>517</v>
+      </c>
+      <c r="M88" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>519</v>
+      </c>
+      <c r="B89" t="s">
+        <v>520</v>
+      </c>
+      <c r="C89" t="s">
+        <v>35</v>
+      </c>
+      <c r="D89" t="s">
+        <v>521</v>
+      </c>
+      <c r="E89" t="s">
+        <v>412</v>
+      </c>
+      <c r="F89" t="s">
+        <v>18</v>
+      </c>
+      <c r="G89" t="s">
+        <v>19</v>
+      </c>
+      <c r="H89" t="s">
+        <v>61</v>
+      </c>
+      <c r="I89" t="s">
+        <v>21</v>
+      </c>
+      <c r="J89" t="s">
+        <v>30</v>
+      </c>
+      <c r="K89" t="s">
+        <v>23</v>
+      </c>
+      <c r="L89" t="s">
+        <v>522</v>
+      </c>
+      <c r="M89" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>524</v>
+      </c>
+      <c r="B90" t="s">
+        <v>525</v>
+      </c>
+      <c r="C90" t="s">
+        <v>35</v>
+      </c>
+      <c r="D90" t="s">
+        <v>526</v>
+      </c>
+      <c r="E90" t="s">
+        <v>467</v>
+      </c>
+      <c r="F90" t="s">
+        <v>18</v>
+      </c>
+      <c r="G90" t="s">
+        <v>19</v>
+      </c>
+      <c r="H90" t="s">
+        <v>61</v>
+      </c>
+      <c r="I90" t="s">
+        <v>21</v>
+      </c>
+      <c r="J90" t="s">
+        <v>88</v>
+      </c>
+      <c r="K90" t="s">
+        <v>23</v>
+      </c>
+      <c r="L90" t="s">
+        <v>527</v>
+      </c>
+      <c r="M90" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>529</v>
+      </c>
+      <c r="B91" t="s">
+        <v>530</v>
+      </c>
+      <c r="C91" t="s">
+        <v>35</v>
+      </c>
+      <c r="D91" t="s">
+        <v>531</v>
+      </c>
+      <c r="E91" t="s">
+        <v>532</v>
+      </c>
+      <c r="F91" t="s">
+        <v>18</v>
+      </c>
+      <c r="G91" t="s">
+        <v>19</v>
+      </c>
+      <c r="H91" t="s">
+        <v>269</v>
+      </c>
+      <c r="I91" t="s">
+        <v>21</v>
+      </c>
+      <c r="J91" t="s">
+        <v>30</v>
+      </c>
+      <c r="K91" t="s">
+        <v>23</v>
+      </c>
+      <c r="L91" t="s">
+        <v>533</v>
+      </c>
+      <c r="M91" t="s">
+        <v>534</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
